--- a/src/width_txt/Разрядность_элементов_адаптивного_фильтра_АЦП_№1.xlsx
+++ b/src/width_txt/Разрядность_элементов_адаптивного_фильтра_АЦП_№1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="64" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="96" uniqueCount="8">
   <si>
     <t>Row</t>
   </si>
@@ -106,10 +106,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="C2" s="0">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -117,10 +117,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="C3" s="0">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -128,10 +128,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C4" s="0">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -139,10 +139,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C5" s="0">
-        <v>85</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -150,10 +150,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C6" s="0">
-        <v>85</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/src/width_txt/Разрядность_элементов_адаптивного_фильтра_АЦП_№1.xlsx
+++ b/src/width_txt/Разрядность_элементов_адаптивного_фильтра_АЦП_№1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="96" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="806" uniqueCount="33">
   <si>
     <t>Row</t>
   </si>
@@ -37,6 +37,81 @@
   </si>
   <si>
     <t>Sum_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>Sum1_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>Sum2_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>Sum3_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>Sum4_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>Sum5_adaptive_total_width</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
 </sst>
 </file>
@@ -82,12 +157,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
     <col min="2" max="2" width="30.85546875" customWidth="true"/>
-    <col min="3" max="3" width="25" customWidth="true"/>
+    <col min="3" max="3" width="26" customWidth="true"/>
+    <col min="4" max="4" width="26" customWidth="true"/>
+    <col min="5" max="5" width="26" customWidth="true"/>
+    <col min="6" max="6" width="26" customWidth="true"/>
+    <col min="7" max="7" width="26" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -98,7 +177,19 @@
         <v>6</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2">
@@ -109,7 +200,19 @@
         <v>34</v>
       </c>
       <c r="C2" s="0">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D2" s="0">
+        <v>33</v>
+      </c>
+      <c r="E2" s="0">
+        <v>32</v>
+      </c>
+      <c r="F2" s="0">
+        <v>32</v>
+      </c>
+      <c r="G2" s="0">
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -120,7 +223,19 @@
         <v>34</v>
       </c>
       <c r="C3" s="0">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D3" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3" s="0">
+        <v>32</v>
+      </c>
+      <c r="F3" s="0">
+        <v>32</v>
+      </c>
+      <c r="G3" s="0">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -131,7 +246,19 @@
         <v>34</v>
       </c>
       <c r="C4" s="0">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D4" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" s="0">
+        <v>32</v>
+      </c>
+      <c r="G4" s="0">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -142,7 +269,19 @@
         <v>34</v>
       </c>
       <c r="C5" s="0">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="D5" s="0">
+        <v>33</v>
+      </c>
+      <c r="E5" s="0">
+        <v>32</v>
+      </c>
+      <c r="F5" s="0">
+        <v>32</v>
+      </c>
+      <c r="G5" s="0">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -155,6 +294,478 @@
       <c r="C6" s="0">
         <v>33</v>
       </c>
+      <c r="D6" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" s="0">
+        <v>32</v>
+      </c>
+      <c r="F6" s="0">
+        <v>32</v>
+      </c>
+      <c r="G6" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="0">
+        <v>34</v>
+      </c>
+      <c r="C7" s="0">
+        <v>33</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="0">
+        <v>34</v>
+      </c>
+      <c r="C8" s="0">
+        <v>33</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="0">
+        <v>33</v>
+      </c>
+      <c r="C9" s="0">
+        <v>33</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="0">
+        <v>33</v>
+      </c>
+      <c r="C10" s="0">
+        <v>33</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="0">
+        <v>33</v>
+      </c>
+      <c r="C11" s="0">
+        <v>33</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="0">
+        <v>33</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="0">
+        <v>32</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="0">
+        <v>32</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="0">
+        <v>32</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="0">
+        <v>32</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="0">
+        <v>32</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="0">
+        <v>32</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="0">
+        <v>32</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="0">
+        <v>32</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0">
+        <v>0</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="0">
+        <v>32</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0">
+        <v>0</v>
+      </c>
+      <c r="G21" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="0">
+        <v>32</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0">
+        <v>0</v>
+      </c>
+      <c r="G22" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="0">
+        <v>32</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0">
+        <v>0</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="0">
+        <v>32</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="0">
+        <v>32</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="0">
+        <v>32</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
